--- a/astro-site/public/dl/guia-panaderia-obrador/cash-flow-break-even.xlsx
+++ b/astro-site/public/dl/guia-panaderia-obrador/cash-flow-break-even.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow 24m" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Cash Flow 24m'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -448,7 +450,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -477,6 +479,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -758,59 +761,59 @@
       </c>
       <c r="B8">
         <f>SUM(B4:B7)</f>
-        <v/>
+        <v>-2800.0</v>
       </c>
       <c r="C8">
         <f>SUM(C4:C7)</f>
-        <v/>
+        <v>-400.0</v>
       </c>
       <c r="D8">
         <f>SUM(D4:D7)</f>
-        <v/>
+        <v>2000.0</v>
       </c>
       <c r="E8">
         <f>SUM(E4:E7)</f>
-        <v/>
+        <v>3600.0</v>
       </c>
       <c r="F8">
         <f>SUM(F4:F7)</f>
-        <v/>
+        <v>4800.0</v>
       </c>
       <c r="G8">
         <f>SUM(G4:G7)</f>
-        <v/>
+        <v>6000.0</v>
       </c>
       <c r="H8">
         <f>SUM(H4:H7)</f>
-        <v/>
+        <v>7200.0</v>
       </c>
       <c r="I8">
         <f>SUM(I4:I7)</f>
-        <v/>
+        <v>8400.0</v>
       </c>
       <c r="J8">
         <f>SUM(J4:J7)</f>
-        <v/>
+        <v>9200.0</v>
       </c>
       <c r="K8">
         <f>SUM(K4:K7)</f>
-        <v/>
+        <v>10000.0</v>
       </c>
       <c r="L8">
         <f>SUM(L4:L7)</f>
-        <v/>
+        <v>10800.0</v>
       </c>
       <c r="M8">
         <f>SUM(M4:M7)</f>
-        <v/>
+        <v>11600.0</v>
       </c>
       <c r="N8">
         <f>SUM(N4:N7)</f>
-        <v/>
+        <v>70400.0</v>
       </c>
       <c r="O8">
         <f>SUM(O4:O7)</f>
-        <v/>
+        <v>113725.0</v>
       </c>
     </row>
     <row r="9">
@@ -822,19 +825,6 @@
       <c r="B9" t="n">
         <v>-145000</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -844,59 +834,59 @@
       </c>
       <c r="B10">
         <f>B8+B9</f>
-        <v/>
+        <v>-147800.0</v>
       </c>
       <c r="C10">
         <f>C8+C9</f>
-        <v/>
+        <v>-400.0</v>
       </c>
       <c r="D10">
         <f>D8+D9</f>
-        <v/>
+        <v>2000.0</v>
       </c>
       <c r="E10">
         <f>E8+E9</f>
-        <v/>
+        <v>3600.0</v>
       </c>
       <c r="F10">
         <f>F8+F9</f>
-        <v/>
+        <v>4800.0</v>
       </c>
       <c r="G10">
         <f>G8+G9</f>
-        <v/>
+        <v>6000.0</v>
       </c>
       <c r="H10">
         <f>H8+H9</f>
-        <v/>
+        <v>7200.0</v>
       </c>
       <c r="I10">
         <f>I8+I9</f>
-        <v/>
+        <v>8400.0</v>
       </c>
       <c r="J10">
         <f>J8+J9</f>
-        <v/>
+        <v>9200.0</v>
       </c>
       <c r="K10">
         <f>K8+K9</f>
-        <v/>
+        <v>10000.0</v>
       </c>
       <c r="L10">
         <f>L8+L9</f>
-        <v/>
+        <v>10800.0</v>
       </c>
       <c r="M10">
         <f>M8+M9</f>
-        <v/>
+        <v>11600.0</v>
       </c>
       <c r="N10">
         <f>N8+N9</f>
-        <v/>
+        <v>70400.0</v>
       </c>
       <c r="O10">
         <f>O8</f>
-        <v/>
+        <v>113725.0</v>
       </c>
     </row>
     <row r="11">
@@ -907,68 +897,68 @@
       </c>
       <c r="B11">
         <f>B10</f>
-        <v/>
+        <v>-147800.0</v>
       </c>
       <c r="C11">
         <f>B11+C10</f>
-        <v/>
+        <v>-148200.0</v>
       </c>
       <c r="D11">
         <f>C11+D10</f>
-        <v/>
+        <v>-146200.0</v>
       </c>
       <c r="E11">
         <f>D11+E10</f>
-        <v/>
+        <v>-142600.0</v>
       </c>
       <c r="F11">
         <f>E11+F10</f>
-        <v/>
+        <v>-137800.0</v>
       </c>
       <c r="G11">
         <f>F11+G10</f>
-        <v/>
+        <v>-131800.0</v>
       </c>
       <c r="H11">
         <f>G11+H10</f>
-        <v/>
+        <v>-124600.0</v>
       </c>
       <c r="I11">
         <f>H11+I10</f>
-        <v/>
+        <v>-116200.0</v>
       </c>
       <c r="J11">
         <f>I11+J10</f>
-        <v/>
+        <v>-107000.0</v>
       </c>
       <c r="K11">
         <f>J11+K10</f>
-        <v/>
+        <v>-97000.0</v>
       </c>
       <c r="L11">
         <f>K11+L10</f>
-        <v/>
+        <v>-86200.0</v>
       </c>
       <c r="M11">
         <f>L11+M10</f>
-        <v/>
+        <v>-74600.0</v>
       </c>
       <c r="N11">
         <f>M11</f>
-        <v/>
+        <v>-74600.0</v>
       </c>
       <c r="O11">
         <f>N11+O8</f>
-        <v/>
-      </c>
-    </row>
+        <v>39125.0</v>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>Break-even alcanzado mes:</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>M10-M12 (realista)</t>
@@ -984,6 +974,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>